--- a/output/Data and Chart Outputs/japan_mof_energy_imports_monthly.xlsx
+++ b/output/Data and Chart Outputs/japan_mof_energy_imports_monthly.xlsx
@@ -195,12 +195,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$55</f>
+              <f>'Chart'!$A$2:$A$57</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$B$2:$B$55</f>
+              <f>'Chart'!$B$2:$B$57</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -332,12 +332,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - Coal and LPG imports'!$A$2:$A$55</f>
+              <f>'Chart - Coal and LPG imports'!$A$2:$A$57</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - Coal and LPG imports'!$B$2:$B$55</f>
+              <f>'Chart - Coal and LPG imports'!$B$2:$B$57</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -368,12 +368,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - Coal and LPG imports'!$A$2:$A$55</f>
+              <f>'Chart - Coal and LPG imports'!$A$2:$A$57</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - Coal and LPG imports'!$C$2:$C$55</f>
+              <f>'Chart - Coal and LPG imports'!$C$2:$C$57</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -404,12 +404,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - Coal and LPG imports'!$A$2:$A$55</f>
+              <f>'Chart - Coal and LPG imports'!$A$2:$A$57</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - Coal and LPG imports'!$D$2:$D$55</f>
+              <f>'Chart - Coal and LPG imports'!$D$2:$D$57</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -545,12 +545,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - Crude oil imports'!$A$2:$A$55</f>
+              <f>'Chart - Crude oil imports'!$A$2:$A$57</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - Crude oil imports'!$B$2:$B$55</f>
+              <f>'Chart - Crude oil imports'!$B$2:$B$57</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1071,7 +1071,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B55"/>
+  <dimension ref="A1:B57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1499,25 +1499,41 @@
     </row>
     <row r="53">
       <c r="A53" s="3" t="n">
-        <v>46174</v>
+        <v>46113</v>
       </c>
       <c r="B53" t="n">
-        <v>4.718</v>
+        <v>4.269</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="n">
-        <v>46204</v>
+        <v>46143</v>
       </c>
       <c r="B54" t="n">
-        <v>5.014</v>
+        <v>3.96</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="n">
+        <v>46174</v>
+      </c>
+      <c r="B55" t="n">
+        <v>4.718</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B56" t="n">
+        <v>5.014</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="n">
         <v>46235</v>
       </c>
-      <c r="B55" t="n">
+      <c r="B57" t="n">
         <v>4.99</v>
       </c>
     </row>
@@ -1533,7 +1549,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D55"/>
+  <dimension ref="A1:D57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -2277,43 +2293,71 @@
     </row>
     <row r="53">
       <c r="A53" s="3" t="n">
-        <v>46174</v>
+        <v>46113</v>
       </c>
       <c r="B53" t="n">
-        <v>11.76</v>
+        <v>12.118</v>
       </c>
       <c r="C53" t="n">
-        <v>7.148</v>
+        <v>7.102</v>
       </c>
       <c r="D53" t="n">
-        <v>0.647</v>
+        <v>0.8149999999999999</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="n">
-        <v>46204</v>
+        <v>46143</v>
       </c>
       <c r="B54" t="n">
-        <v>14.872</v>
+        <v>11.541</v>
       </c>
       <c r="C54" t="n">
-        <v>8.811</v>
+        <v>6.601</v>
       </c>
       <c r="D54" t="n">
-        <v>0.705</v>
+        <v>0.679</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="n">
+        <v>46174</v>
+      </c>
+      <c r="B55" t="n">
+        <v>11.76</v>
+      </c>
+      <c r="C55" t="n">
+        <v>7.148</v>
+      </c>
+      <c r="D55" t="n">
+        <v>0.647</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B56" t="n">
+        <v>14.872</v>
+      </c>
+      <c r="C56" t="n">
+        <v>8.811</v>
+      </c>
+      <c r="D56" t="n">
+        <v>0.705</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="n">
         <v>46235</v>
       </c>
-      <c r="B55" t="n">
+      <c r="B57" t="n">
         <v>14.857</v>
       </c>
-      <c r="C55" t="n">
+      <c r="C57" t="n">
         <v>9.092000000000001</v>
       </c>
-      <c r="D55" t="n">
+      <c r="D57" t="n">
         <v>0.613</v>
       </c>
     </row>
@@ -2329,7 +2373,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B55"/>
+  <dimension ref="A1:B57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -2757,25 +2801,41 @@
     </row>
     <row r="53">
       <c r="A53" s="3" t="n">
-        <v>46174</v>
+        <v>46113</v>
       </c>
       <c r="B53" t="n">
-        <v>8.816000000000001</v>
+        <v>4.48</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="n">
-        <v>46204</v>
+        <v>46143</v>
       </c>
       <c r="B54" t="n">
-        <v>12.106</v>
+        <v>4.727</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="n">
+        <v>46174</v>
+      </c>
+      <c r="B55" t="n">
+        <v>8.816000000000001</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B56" t="n">
+        <v>12.106</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="n">
         <v>46235</v>
       </c>
-      <c r="B55" t="n">
+      <c r="B57" t="n">
         <v>11.594</v>
       </c>
     </row>
@@ -2791,7 +2851,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H55"/>
+  <dimension ref="A1:H57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4164,79 +4224,131 @@
     </row>
     <row r="53">
       <c r="A53" s="4" t="n">
-        <v>46174</v>
+        <v>46113</v>
       </c>
       <c r="B53" t="n">
-        <v>4718</v>
+        <v>4269</v>
       </c>
       <c r="C53" t="n">
-        <v>434502</v>
+        <v>379592</v>
       </c>
       <c r="D53" t="n">
-        <v>8816</v>
+        <v>4480</v>
       </c>
       <c r="E53" t="n">
-        <v>1037875</v>
+        <v>457296</v>
       </c>
       <c r="F53" t="n">
-        <v>647</v>
+        <v>815</v>
       </c>
       <c r="G53" t="n">
-        <v>11760</v>
+        <v>12118</v>
       </c>
       <c r="H53" t="n">
-        <v>7148</v>
+        <v>7102</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="n">
-        <v>46204</v>
+        <v>46143</v>
       </c>
       <c r="B54" t="n">
-        <v>5014</v>
+        <v>3960</v>
       </c>
       <c r="C54" t="n">
-        <v>547519</v>
+        <v>391946</v>
       </c>
       <c r="D54" t="n">
-        <v>12106</v>
+        <v>4727</v>
       </c>
       <c r="E54" t="n">
-        <v>1409133</v>
+        <v>538904</v>
       </c>
       <c r="F54" t="n">
-        <v>705</v>
+        <v>679</v>
       </c>
       <c r="G54" t="n">
-        <v>14872</v>
+        <v>11541</v>
       </c>
       <c r="H54" t="n">
-        <v>8811</v>
+        <v>6601</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="n">
+        <v>46174</v>
+      </c>
+      <c r="B55" t="n">
+        <v>4718</v>
+      </c>
+      <c r="C55" t="n">
+        <v>434502</v>
+      </c>
+      <c r="D55" t="n">
+        <v>8816</v>
+      </c>
+      <c r="E55" t="n">
+        <v>1037875</v>
+      </c>
+      <c r="F55" t="n">
+        <v>647</v>
+      </c>
+      <c r="G55" t="n">
+        <v>11760</v>
+      </c>
+      <c r="H55" t="n">
+        <v>7148</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B56" t="n">
+        <v>5014</v>
+      </c>
+      <c r="C56" t="n">
+        <v>547519</v>
+      </c>
+      <c r="D56" t="n">
+        <v>12106</v>
+      </c>
+      <c r="E56" t="n">
+        <v>1409133</v>
+      </c>
+      <c r="F56" t="n">
+        <v>705</v>
+      </c>
+      <c r="G56" t="n">
+        <v>14872</v>
+      </c>
+      <c r="H56" t="n">
+        <v>8811</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="n">
         <v>46235</v>
       </c>
-      <c r="B55" t="n">
+      <c r="B57" t="n">
         <v>4990</v>
       </c>
-      <c r="C55" t="n">
+      <c r="C57" t="n">
         <v>588194</v>
       </c>
-      <c r="D55" t="n">
+      <c r="D57" t="n">
         <v>11594</v>
       </c>
-      <c r="E55" t="n">
+      <c r="E57" t="n">
         <v>1190519</v>
       </c>
-      <c r="F55" t="n">
+      <c r="F57" t="n">
         <v>613</v>
       </c>
-      <c r="G55" t="n">
+      <c r="G57" t="n">
         <v>14857</v>
       </c>
-      <c r="H55" t="n">
+      <c r="H57" t="n">
         <v>9092</v>
       </c>
     </row>
@@ -4251,7 +4363,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D55"/>
+  <dimension ref="A1:D57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5196,11 +5308,11 @@
     </row>
     <row r="53">
       <c r="A53" s="4" t="n">
-        <v>46174</v>
+        <v>46113</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>trade-st/2026/2026066.pdf</t>
+          <t>trade-st/2026/2026046.pdf</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -5208,17 +5320,17 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>令和 8 年 6月分貿易統計（確報）</t>
+          <t>令和 8 年 4月分貿易統計（確報）</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="n">
-        <v>46204</v>
+        <v>46143</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>trade-st/2026/2026076.pdf</t>
+          <t>trade-st/2026/2026056.pdf</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -5226,23 +5338,59 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>令和 8 年 7月分貿易統計（確報）</t>
+          <t>令和 8 年 5月分貿易統計（確報）</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="n">
+        <v>46174</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>trade-st/2026/2026066.pdf</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>6</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>令和 8 年 6月分貿易統計（確報）</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>trade-st/2026/2026076.pdf</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>6</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>令和 8 年 7月分貿易統計（確報）</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="n">
         <v>46235</v>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B57" t="inlineStr">
         <is>
           <t>trade-st/2026/2026085.pdf</t>
         </is>
       </c>
-      <c r="C55" t="n">
+      <c r="C57" t="n">
         <v>5</v>
       </c>
-      <c r="D55" t="inlineStr">
+      <c r="D57" t="inlineStr">
         <is>
           <t>令和 8 年 8 月分貿易統計（輸出確報；輸入速報（9桁））</t>
         </is>

--- a/output/Data and Chart Outputs/japan_mof_energy_imports_monthly.xlsx
+++ b/output/Data and Chart Outputs/japan_mof_energy_imports_monthly.xlsx
@@ -159,7 +159,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>Japan LNG imports (Ministry of Finance customs statistics) (to Aug/26)</a:t>
+              <a:t>Japan LNG imports (Ministry of Finance customs statistics) (to Sep/26)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -195,12 +195,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$57</f>
+              <f>'Chart'!$A$2:$A$58</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$B$2:$B$57</f>
+              <f>'Chart'!$B$2:$B$58</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -296,7 +296,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>Japan coal and LPG imports (Ministry of Finance customs statistics) (to Aug/26)</a:t>
+              <a:t>Japan coal and LPG imports (Ministry of Finance customs statistics) (to Sep/26)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -332,12 +332,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - Coal and LPG imports'!$A$2:$A$57</f>
+              <f>'Chart - Coal and LPG imports'!$A$2:$A$58</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - Coal and LPG imports'!$B$2:$B$57</f>
+              <f>'Chart - Coal and LPG imports'!$B$2:$B$58</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -368,12 +368,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - Coal and LPG imports'!$A$2:$A$57</f>
+              <f>'Chart - Coal and LPG imports'!$A$2:$A$58</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - Coal and LPG imports'!$C$2:$C$57</f>
+              <f>'Chart - Coal and LPG imports'!$C$2:$C$58</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -404,12 +404,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - Coal and LPG imports'!$A$2:$A$57</f>
+              <f>'Chart - Coal and LPG imports'!$A$2:$A$58</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - Coal and LPG imports'!$D$2:$D$57</f>
+              <f>'Chart - Coal and LPG imports'!$D$2:$D$58</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -509,7 +509,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>Japan crude oil imports (Ministry of Finance customs statistics) (to Aug/26)</a:t>
+              <a:t>Japan crude oil imports (Ministry of Finance customs statistics) (to Sep/26)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -545,12 +545,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - Crude oil imports'!$A$2:$A$57</f>
+              <f>'Chart - Crude oil imports'!$A$2:$A$58</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - Crude oil imports'!$B$2:$B$57</f>
+              <f>'Chart - Crude oil imports'!$B$2:$B$58</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1071,7 +1071,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B57"/>
+  <dimension ref="A1:B58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1535,6 +1535,14 @@
       </c>
       <c r="B57" t="n">
         <v>4.99</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B58" t="n">
+        <v>4.779</v>
       </c>
     </row>
   </sheetData>
@@ -1549,7 +1557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D57"/>
+  <dimension ref="A1:D58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -2359,6 +2367,20 @@
       </c>
       <c r="D57" t="n">
         <v>0.613</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B58" t="n">
+        <v>13.484</v>
+      </c>
+      <c r="C58" t="n">
+        <v>8.846</v>
+      </c>
+      <c r="D58" t="n">
+        <v>0.632</v>
       </c>
     </row>
   </sheetData>
@@ -2373,7 +2395,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B57"/>
+  <dimension ref="A1:B58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -2837,6 +2859,14 @@
       </c>
       <c r="B57" t="n">
         <v>11.594</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B58" t="n">
+        <v>11.166</v>
       </c>
     </row>
   </sheetData>
@@ -2851,7 +2881,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H57"/>
+  <dimension ref="A1:H58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4350,6 +4380,32 @@
       </c>
       <c r="H57" t="n">
         <v>9092</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B58" t="n">
+        <v>4779</v>
+      </c>
+      <c r="C58" t="n">
+        <v>590561</v>
+      </c>
+      <c r="D58" t="n">
+        <v>11166</v>
+      </c>
+      <c r="E58" t="n">
+        <v>1110219</v>
+      </c>
+      <c r="F58" t="n">
+        <v>632</v>
+      </c>
+      <c r="G58" t="n">
+        <v>13484</v>
+      </c>
+      <c r="H58" t="n">
+        <v>8846</v>
       </c>
     </row>
   </sheetData>
@@ -4363,7 +4419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D57"/>
+  <dimension ref="A1:D58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5396,6 +5452,24 @@
         </is>
       </c>
     </row>
+    <row r="58">
+      <c r="A58" s="4" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>trade-st/2026/2026094.pdf</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>4</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>令和 8 年 9月分貿易統計（速報）</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
